--- a/output/pdf_financials_xlsx/ERO.xlsx
+++ b/output/pdf_financials_xlsx/ERO.xlsx
@@ -2676,13 +2676,13 @@
         </is>
       </c>
       <c r="H61" s="3" t="n">
-        <v>28.952</v>
+        <v>1282.265</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>29.733</v>
+        <v>1304.886</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>36.696</v>
+        <v>1613.797</v>
       </c>
     </row>
     <row r="62">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OtherNonCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
